--- a/doc/board.xlsx
+++ b/doc/board.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\daten\dev\chess\java.chess.perft\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\private\dev\java.chess.perft\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63FA7A5-9235-4FEB-AB19-C695C11AD4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDCFCFD-7054-4BB1-BD67-0174D68241F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4090" yWindow="5670" windowWidth="15500" windowHeight="10390" xr2:uid="{61C95BD5-E292-41FC-A0C1-C26B0894341E}"/>
+    <workbookView xWindow="-105" yWindow="8550" windowWidth="16245" windowHeight="14940" xr2:uid="{61C95BD5-E292-41FC-A0C1-C26B0894341E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
   <si>
     <t>a</t>
   </si>
@@ -92,23 +92,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -123,21 +138,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -153,7 +168,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -469,14 +484,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C01B90-9D68-45F1-945A-696AA023B3A0}">
-  <dimension ref="B3:U11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B3:U23"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="11" width="3.90625" customWidth="1"/>
-    <col min="13" max="21" width="3.90625" customWidth="1"/>
+    <col min="2" max="11" width="3.85546875" customWidth="1"/>
+    <col min="13" max="21" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -529,488 +544,488 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="D4" s="5">
-        <f>C4+1</f>
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:J11" si="0">C4+1</f>
         <v>1</v>
       </c>
-      <c r="E4" s="5">
-        <f>D4+1</f>
+      <c r="E4" s="1">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F4" s="5">
-        <f>E4+1</f>
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G4" s="5">
-        <f>F4+1</f>
+      <c r="G4" s="1">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H4" s="5">
-        <f>G4+1</f>
+      <c r="H4" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I4" s="5">
-        <f>H4+1</f>
+      <c r="I4" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="J4" s="5">
-        <f>I4+1</f>
+      <c r="J4" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="K4" s="1"/>
       <c r="M4" s="2">
-        <f t="shared" ref="M4:M9" si="0">M5+1</f>
+        <f t="shared" ref="M4:M9" si="1">M5+1</f>
         <v>8</v>
       </c>
-      <c r="N4" s="1">
-        <f t="shared" ref="N4:S4" si="1">O4-1</f>
+      <c r="N4" s="4">
+        <f t="shared" ref="N4:S4" si="2">O4-1</f>
         <v>56</v>
       </c>
-      <c r="O4" s="1">
-        <f t="shared" si="1"/>
+      <c r="O4" s="4">
+        <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="P4" s="1">
-        <f t="shared" si="1"/>
+      <c r="P4" s="4">
+        <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="Q4" s="1">
-        <f t="shared" si="1"/>
+      <c r="Q4" s="4">
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="R4" s="1">
-        <f t="shared" si="1"/>
+      <c r="R4" s="4">
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="S4" s="1">
-        <f t="shared" si="1"/>
+      <c r="S4" s="4">
+        <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="T4" s="1">
+      <c r="T4" s="4">
         <f>U4-1</f>
         <v>62</v>
       </c>
-      <c r="U4" s="1">
+      <c r="U4" s="4">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
-        <f>B4+1</f>
+        <f t="shared" ref="B5:B11" si="3">B4+1</f>
         <v>2</v>
       </c>
-      <c r="C5" s="5">
-        <f>J4+1</f>
+      <c r="C5" s="1">
+        <f t="shared" ref="C5:C11" si="4">J4+1</f>
         <v>8</v>
       </c>
-      <c r="D5" s="5">
-        <f>C5+1</f>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E5" s="5">
-        <f>D5+1</f>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F5" s="5">
-        <f>E5+1</f>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="G5" s="5">
-        <f>F5+1</f>
+      <c r="G5" s="1">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H5" s="5">
-        <f>G5+1</f>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="I5" s="5">
-        <f>H5+1</f>
+      <c r="I5" s="1">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="J5" s="5">
-        <f>I5+1</f>
+      <c r="J5" s="1">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="K5" s="1"/>
       <c r="M5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="N5" s="1">
-        <f t="shared" ref="N5:T11" si="2">O5-1</f>
+      <c r="N5" s="4">
+        <f t="shared" ref="N5:T11" si="5">O5-1</f>
         <v>48</v>
       </c>
-      <c r="O5" s="1">
-        <f t="shared" si="2"/>
+      <c r="O5" s="4">
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
-      <c r="P5" s="1">
-        <f t="shared" si="2"/>
+      <c r="P5" s="4">
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="Q5" s="1">
-        <f t="shared" si="2"/>
+      <c r="Q5" s="4">
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
-      <c r="R5" s="1">
-        <f t="shared" si="2"/>
+      <c r="R5" s="4">
+        <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="S5" s="1">
-        <f t="shared" si="2"/>
+      <c r="S5" s="4">
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
-      <c r="T5" s="1">
-        <f t="shared" si="2"/>
+      <c r="T5" s="4">
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
-      <c r="U5" s="1">
-        <f>N4-1</f>
+      <c r="U5" s="4">
+        <f t="shared" ref="U5:U11" si="6">N4-1</f>
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
-        <f>B5+1</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="C6" s="5">
-        <f>J5+1</f>
+      <c r="C6" s="1">
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="D6" s="5">
-        <f>C6+1</f>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E6" s="5">
-        <f>D6+1</f>
+      <c r="E6" s="1">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="F6" s="5">
-        <f>E6+1</f>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G6" s="5">
-        <f>F6+1</f>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H6" s="5">
-        <f>G6+1</f>
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="I6" s="5">
-        <f>H6+1</f>
+      <c r="I6" s="1">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="J6" s="5">
-        <f>I6+1</f>
+      <c r="J6" s="1">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="K6" s="1"/>
       <c r="M6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N6" s="5">
-        <f t="shared" si="2"/>
+      <c r="N6" s="4">
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="O6" s="5">
-        <f t="shared" si="2"/>
+      <c r="O6" s="4">
+        <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="P6" s="5">
-        <f t="shared" si="2"/>
+      <c r="P6" s="6">
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
-      <c r="Q6" s="5">
-        <f t="shared" si="2"/>
+      <c r="Q6" s="4">
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
-      <c r="R6" s="5">
-        <f t="shared" si="2"/>
+      <c r="R6" s="4">
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
-      <c r="S6" s="5">
-        <f t="shared" si="2"/>
+      <c r="S6" s="4">
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="T6" s="5">
-        <f t="shared" si="2"/>
+      <c r="T6" s="4">
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
-      <c r="U6" s="5">
-        <f>N5-1</f>
+      <c r="U6" s="4">
+        <f t="shared" si="6"/>
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
-        <f>B6+1</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="C7" s="5">
-        <f>J6+1</f>
+      <c r="C7" s="1">
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="D7" s="5">
-        <f>C7+1</f>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="E7" s="5">
-        <f>D7+1</f>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="F7" s="5">
-        <f>E7+1</f>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="G7" s="5">
-        <f>F7+1</f>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="H7" s="5">
-        <f>G7+1</f>
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="I7" s="5">
-        <f>H7+1</f>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="J7" s="5">
-        <f>I7+1</f>
+      <c r="J7" s="1">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="K7" s="1"/>
       <c r="M7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N7" s="5">
-        <f t="shared" si="2"/>
+      <c r="N7" s="4">
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="O7" s="5">
-        <f t="shared" si="2"/>
+      <c r="O7" s="4">
+        <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="P7" s="5">
-        <f t="shared" si="2"/>
+      <c r="P7" s="4">
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
-      <c r="Q7" s="5">
-        <f t="shared" si="2"/>
+      <c r="Q7" s="4">
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="R7" s="5">
-        <f t="shared" si="2"/>
+      <c r="R7" s="3">
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="S7" s="5">
-        <f t="shared" si="2"/>
+      <c r="S7" s="4">
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
-      <c r="T7" s="5">
-        <f t="shared" si="2"/>
+      <c r="T7" s="4">
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="U7" s="5">
-        <f>N6-1</f>
+      <c r="U7" s="4">
+        <f t="shared" si="6"/>
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <f>B7+1</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="C8" s="6">
-        <f>J7+1</f>
+      <c r="C8" s="1">
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="D8" s="5">
-        <f>C8+1</f>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="E8" s="5">
-        <f>D8+1</f>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="F8" s="5">
-        <f>E8+1</f>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="G8" s="5">
-        <f>F8+1</f>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="H8" s="5">
-        <f>G8+1</f>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="I8" s="5">
-        <f>H8+1</f>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="J8" s="5">
-        <f>I8+1</f>
+      <c r="J8" s="1">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="K8" s="1"/>
       <c r="M8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="N8" s="5">
-        <f t="shared" si="2"/>
+      <c r="N8" s="4">
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="O8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="P8" s="5">
-        <f t="shared" si="2"/>
+      <c r="P8" s="4">
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="Q8" s="5">
-        <f t="shared" si="2"/>
+      <c r="Q8" s="4">
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
-      <c r="R8" s="5">
-        <f t="shared" si="2"/>
+      <c r="R8" s="4">
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="S8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="T8" s="4">
-        <f t="shared" si="2"/>
+      <c r="T8" s="6">
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="U8" s="5">
-        <f>N7-1</f>
+      <c r="U8" s="4">
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <f>B8+1</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="C9" s="5">
-        <f>J8+1</f>
+      <c r="C9" s="1">
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="D9" s="5">
-        <f>C9+1</f>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="E9" s="5">
-        <f>D9+1</f>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="F9" s="5">
-        <f>E9+1</f>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="G9" s="5">
-        <f>F9+1</f>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="H9" s="5">
-        <f>G9+1</f>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="I9" s="5">
-        <f>H9+1</f>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="J9" s="5">
-        <f>I9+1</f>
+      <c r="J9" s="1">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="K9" s="1"/>
       <c r="M9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N9" s="3">
-        <f t="shared" si="2"/>
+      <c r="N9" s="4">
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="O9" s="5">
-        <f t="shared" si="2"/>
+      <c r="O9" s="4">
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="P9" s="5">
-        <f t="shared" si="2"/>
+      <c r="P9" s="4">
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="Q9" s="5">
-        <f t="shared" si="2"/>
+      <c r="Q9" s="4">
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="R9" s="5">
-        <f t="shared" si="2"/>
+      <c r="R9" s="4">
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="S9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="T9" s="5">
-        <f t="shared" si="2"/>
+      <c r="T9" s="4">
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="U9" s="3">
-        <f>N8-1</f>
+      <c r="U9" s="4">
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
-        <f>B9+1</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="C10" s="5">
-        <f>J9+1</f>
+      <c r="C10" s="1">
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="D10" s="5">
-        <f>C10+1</f>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="E10" s="5">
-        <f>D10+1</f>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="F10" s="5">
-        <f>E10+1</f>
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="G10" s="5">
-        <f>F10+1</f>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="H10" s="5">
-        <f>G10+1</f>
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="I10" s="5">
-        <f>H10+1</f>
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="J10" s="5">
-        <f>I10+1</f>
+      <c r="J10" s="1">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="K10" s="1"/>
@@ -1018,110 +1033,439 @@
         <f>M11+1</f>
         <v>2</v>
       </c>
-      <c r="N10" s="1">
-        <f t="shared" si="2"/>
+      <c r="N10" s="4">
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="O10" s="1">
-        <f t="shared" si="2"/>
+      <c r="O10" s="4">
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="P10" s="1">
-        <f t="shared" si="2"/>
+      <c r="P10" s="4">
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="Q10" s="1">
-        <f t="shared" si="2"/>
+      <c r="Q10" s="4">
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="R10" s="1">
-        <f t="shared" si="2"/>
+      <c r="R10" s="4">
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="S10" s="1">
-        <f t="shared" si="2"/>
+      <c r="S10" s="4">
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="T10" s="1">
-        <f t="shared" si="2"/>
+      <c r="T10" s="4">
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="U10" s="1">
-        <f>N9-1</f>
+      <c r="U10" s="4">
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:21" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
-        <f>B10+1</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <f>J10+1</f>
+      <c r="C11" s="1">
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
-      <c r="D11" s="5">
-        <f>C11+1</f>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="E11" s="5">
-        <f>D11+1</f>
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="F11" s="5">
-        <f>E11+1</f>
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="G11" s="5">
-        <f>F11+1</f>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="H11" s="5">
-        <f>G11+1</f>
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="I11" s="5">
-        <f>H11+1</f>
+      <c r="I11" s="1">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="J11" s="5">
-        <f>I11+1</f>
+      <c r="J11" s="1">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="K11" s="1"/>
       <c r="M11" s="2">
         <v>1</v>
       </c>
-      <c r="N11" s="1">
-        <f t="shared" si="2"/>
+      <c r="N11" s="4">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="1">
-        <f t="shared" si="2"/>
+      <c r="O11" s="4">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="P11" s="1">
-        <f t="shared" si="2"/>
+      <c r="P11" s="4">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="Q11" s="1">
-        <f t="shared" si="2"/>
+      <c r="Q11" s="4">
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="R11" s="1">
-        <f t="shared" si="2"/>
+      <c r="R11" s="5">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="S11" s="1">
-        <f t="shared" si="2"/>
+      <c r="S11" s="4">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="T11" s="1">
-        <f t="shared" si="2"/>
+      <c r="T11" s="4">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="U11" s="1">
-        <f>N10-1</f>
+      <c r="U11" s="4">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M15" s="1"/>
+      <c r="N15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M16" s="2">
+        <f t="shared" ref="M16:M21" si="7">M17+1</f>
+        <v>8</v>
+      </c>
+      <c r="N16" s="4">
+        <f t="shared" ref="N16:N23" si="8">O16-1</f>
+        <v>56</v>
+      </c>
+      <c r="O16" s="4">
+        <f t="shared" ref="O16:O23" si="9">P16-1</f>
+        <v>57</v>
+      </c>
+      <c r="P16" s="4">
+        <f t="shared" ref="P16:P23" si="10">Q16-1</f>
+        <v>58</v>
+      </c>
+      <c r="Q16" s="4">
+        <f t="shared" ref="Q16:Q23" si="11">R16-1</f>
+        <v>59</v>
+      </c>
+      <c r="R16" s="4">
+        <f t="shared" ref="R16:R23" si="12">S16-1</f>
+        <v>60</v>
+      </c>
+      <c r="S16" s="4">
+        <f t="shared" ref="S16:S23" si="13">T16-1</f>
+        <v>61</v>
+      </c>
+      <c r="T16" s="4">
+        <f>U16-1</f>
+        <v>62</v>
+      </c>
+      <c r="U16" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="13:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M17" s="2">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="N17" s="4">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="O17" s="4">
+        <f t="shared" si="9"/>
+        <v>49</v>
+      </c>
+      <c r="P17" s="4">
+        <f t="shared" si="10"/>
+        <v>50</v>
+      </c>
+      <c r="Q17" s="4">
+        <f t="shared" si="11"/>
+        <v>51</v>
+      </c>
+      <c r="R17" s="4">
+        <f t="shared" si="12"/>
+        <v>52</v>
+      </c>
+      <c r="S17" s="4">
+        <f t="shared" si="13"/>
+        <v>53</v>
+      </c>
+      <c r="T17" s="4">
+        <f t="shared" ref="T17:T23" si="14">U17-1</f>
+        <v>54</v>
+      </c>
+      <c r="U17" s="4">
+        <f t="shared" ref="U17:U23" si="15">N16-1</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="13:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M18" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="N18" s="4">
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+      <c r="O18" s="4">
+        <f t="shared" si="9"/>
+        <v>41</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" si="10"/>
+        <v>42</v>
+      </c>
+      <c r="Q18" s="4">
+        <f t="shared" si="11"/>
+        <v>43</v>
+      </c>
+      <c r="R18" s="4">
+        <f t="shared" si="12"/>
+        <v>44</v>
+      </c>
+      <c r="S18" s="4">
+        <f t="shared" si="13"/>
+        <v>45</v>
+      </c>
+      <c r="T18" s="4">
+        <f t="shared" si="14"/>
+        <v>46</v>
+      </c>
+      <c r="U18" s="4">
+        <f t="shared" si="15"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="13:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M19" s="2">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="N19" s="4">
+        <f t="shared" si="8"/>
+        <v>32</v>
+      </c>
+      <c r="O19" s="4">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="P19" s="4">
+        <f t="shared" si="10"/>
+        <v>34</v>
+      </c>
+      <c r="Q19" s="4">
+        <f t="shared" si="11"/>
+        <v>35</v>
+      </c>
+      <c r="R19" s="6">
+        <f t="shared" si="12"/>
+        <v>36</v>
+      </c>
+      <c r="S19" s="4">
+        <f t="shared" si="13"/>
+        <v>37</v>
+      </c>
+      <c r="T19" s="4">
+        <f t="shared" si="14"/>
+        <v>38</v>
+      </c>
+      <c r="U19" s="4">
+        <f t="shared" si="15"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="13:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M20" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="N20" s="4">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="O20" s="4">
+        <f t="shared" si="9"/>
+        <v>25</v>
+      </c>
+      <c r="P20" s="4">
+        <f t="shared" si="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q20" s="4">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="R20" s="4">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="S20" s="5">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="T20" s="4">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="U20" s="4">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="13:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M21" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="N21" s="4">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="O21" s="4">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="P21" s="4">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="Q21" s="4">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="R21" s="4">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="S21" s="5">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="T21" s="4">
+        <f t="shared" si="14"/>
+        <v>22</v>
+      </c>
+      <c r="U21" s="4">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="13:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M22" s="2">
+        <f>M23+1</f>
+        <v>2</v>
+      </c>
+      <c r="N22" s="4">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="O22" s="4">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="P22" s="4">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="Q22" s="4">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="R22" s="4">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="S22" s="4">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="T22" s="4">
+        <f t="shared" si="14"/>
+        <v>14</v>
+      </c>
+      <c r="U22" s="4">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="13:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M23" s="2">
+        <v>1</v>
+      </c>
+      <c r="N23" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="4">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P23" s="4">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="Q23" s="4">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="S23" s="4">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="T23" s="4">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="U23" s="4">
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
